--- a/samples/midlands-rural-electric.xlsx
+++ b/samples/midlands-rural-electric.xlsx
@@ -422,7 +422,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lines. Sample file for Seamline; projects are fictional.</v>
+        <v>Lines. Sample file for Nexxo; projects are fictional.</v>
       </c>
     </row>
     <row r="4">
@@ -596,7 +596,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Substations. Sample file for Seamline; projects are fictional.</v>
+        <v>Substations. Sample file for Nexxo; projects are fictional.</v>
       </c>
     </row>
     <row r="4">
